--- a/github_siteplan_links.xlsx
+++ b/github_siteplan_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPRoyal Mail, Papyrus Road, Peterborough, PE4 5PE.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPRoyal Mail, Papyrus Road, Peterborough, PE4 5PE.png</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPBunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPBunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ.png</t>
         </is>
       </c>
     </row>
@@ -472,235 +472,247 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPYodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPYodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SPSpringhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT</t>
+          <t>SPUnits 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPSpringhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPLink 62, Premier Way South, Normanton, WF6 1GX</t>
+          <t>SPSpringhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPLink 62, Premier Way South, Normanton, WF6 1GX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPSpringhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SP Ash Ridge Road, Almondsbury, BS32 4LB</t>
+          <t>SPLink 62, Premier Way South, Normanton, WF6 1GX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPAsh Ridge Road, Almondsbury, BS32 4LB.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPLink 62, Premier Way South, Normanton, WF6 1GX.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SPUnits 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA</t>
+          <t>SP Ash Ridge Road, Almondsbury, BS32 4LB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnits 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPAsh Ridge Road, Almondsbury, BS32 4LB.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPUniversal Point, Steelmans Road, Wednesbury (WS10 9UZ)</t>
+          <t>SPUnits 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUniversal Point, Steelmans Road, Wednesbury (WS10 9UZ).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPUnits 6-8, Wells Place, Merstham, Redhill, RH1 3AX</t>
+          <t>SPUniversal Point, Steelmans Road, Wednesbury (WS10 9UZ)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnits 6-8, Wells Place, Merstham, Redhill, RH1 3AX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUniversal Point, Steelmans Road, Wednesbury (WS10 9UZ).png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SPUnit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB)</t>
+          <t>SPUnits 6-8, Wells Place, Merstham, Redhill, RH1 3AX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 6-8, Wells Place, Merstham, Redhill, RH1 3AX.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SPCargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF)</t>
+          <t>SPUnit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPCargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB).png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SPUnit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL)</t>
+          <t>SPCargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPCargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF).png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SPDukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS</t>
+          <t>SPUnit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPDukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL).png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SP97-99 Beddington Ln, Croydon (CR0 4TD)</t>
+          <t>SPDukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SP97-99 Beddington Ln, Croydon (CR0 4TD).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPDukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPUnits 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA)</t>
+          <t>SP97-99 Beddington Ln, Croydon (CR0 4TD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnits 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SP97-99 Beddington Ln, Croydon (CR0 4TD).png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SPUnits 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN</t>
+          <t>SPUnits 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnits 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA).png</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPHanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE</t>
+          <t>SPUnits 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPHanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN.png</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SPSinclair Drive, Wellingborough, NN8 6UW</t>
+          <t>SPHanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPSinclair Drive, Wellingborough, NN8 6UW.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPHanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE.png</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SPAxis 40, Athlon Industrial Estate, Wembley, HA0 1YJ</t>
+          <t>SPSinclair Drive, Wellingborough, NN8 6UW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPAxis 40, Athlon Industrial Estate, Wembley, HA0 1YJ.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPSinclair Drive, Wellingborough, NN8 6UW.png</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SPUnits 1, Merlin Park, Stretford, Manchester (M32 0SZ)</t>
+          <t>SPAxis 40, Athlon Industrial Estate, Wembley, HA0 1YJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnits 1, Merlin Park, Stretford, Manchester (M32 0SZ).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPAxis 40, Athlon Industrial Estate, Wembley, HA0 1YJ.png</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SPUnits 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB)</t>
+          <t>SPUnits 1, Merlin Park, Stretford, Manchester (M32 0SZ)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnits 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1, Merlin Park, Stretford, Manchester (M32 0SZ).png</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>SPUnits 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB).png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>SPUnits J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/H1470/KWphotos/main/Images/SPUnits J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN).png</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN).png</t>
         </is>
       </c>
     </row>

--- a/github_siteplan_links.xlsx
+++ b/github_siteplan_links.xlsx
@@ -443,276 +443,276 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SPRoyal Mail, Papyrus Road, Peterborough, PE4 5PE</t>
+          <t>Royal Mail, Papyrus Road, Peterborough, PE4 5PE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPRoyal Mail, Papyrus Road, Peterborough, PE4 5PE.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Royal Mail, Papyrus Road, Peterborough, PE4 5PE.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPBunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ</t>
+          <t>Bunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPBunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Bunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SPYodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX</t>
+          <t>Yodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPYodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Yodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SPUnits 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ</t>
+          <t>Units 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPSpringhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT</t>
+          <t>Springhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPSpringhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Springhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPLink 62, Premier Way South, Normanton, WF6 1GX</t>
+          <t>Link 62, Premier Way South, Normanton, WF6 1GX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPLink 62, Premier Way South, Normanton, WF6 1GX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Link 62, Premier Way South, Normanton, WF6 1GX.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SP Ash Ridge Road, Almondsbury, BS32 4LB</t>
+          <t xml:space="preserve"> Ash Ridge Road, Almondsbury, BS32 4LB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPAsh Ridge Road, Almondsbury, BS32 4LB.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Ash Ridge Road, Almondsbury, BS32 4LB.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPUnits 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA</t>
+          <t>Units 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPUniversal Point, Steelmans Road, Wednesbury (WS10 9UZ)</t>
+          <t>Universal Point, Steelmans Road, Wednesbury (WS10 9UZ)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUniversal Point, Steelmans Road, Wednesbury (WS10 9UZ).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Universal Point, Steelmans Road, Wednesbury (WS10 9UZ).png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SPUnits 6-8, Wells Place, Merstham, Redhill, RH1 3AX</t>
+          <t>Units 6-8, Wells Place, Merstham, Redhill, RH1 3AX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 6-8, Wells Place, Merstham, Redhill, RH1 3AX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 6-8, Wells Place, Merstham, Redhill, RH1 3AX.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SPUnit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB)</t>
+          <t>Unit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Unit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB).png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SPCargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF)</t>
+          <t>Cargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPCargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Cargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF).png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SPUnit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL)</t>
+          <t>Unit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Unit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL).png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SPDukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS</t>
+          <t>Dukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPDukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Dukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SP97-99 Beddington Ln, Croydon (CR0 4TD)</t>
+          <t>97-99 Beddington Ln, Croydon (CR0 4TD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SP97-99 Beddington Ln, Croydon (CR0 4TD).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/97-99 Beddington Ln, Croydon (CR0 4TD).png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SPUnits 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA)</t>
+          <t>Units 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA).png</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPUnits 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN</t>
+          <t>Units 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN.png</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SPHanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE</t>
+          <t>Hanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPHanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Hanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE.png</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SPSinclair Drive, Wellingborough, NN8 6UW</t>
+          <t>Sinclair Drive, Wellingborough, NN8 6UW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPSinclair Drive, Wellingborough, NN8 6UW.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Sinclair Drive, Wellingborough, NN8 6UW.png</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SPAxis 40, Athlon Industrial Estate, Wembley, HA0 1YJ</t>
+          <t>Axis 40, Athlon Industrial Estate, Wembley, HA0 1YJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPAxis 40, Athlon Industrial Estate, Wembley, HA0 1YJ.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Axis 40, Athlon Industrial Estate, Wembley, HA0 1YJ.png</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SPUnits 1, Merlin Park, Stretford, Manchester (M32 0SZ)</t>
+          <t>Units 1, Merlin Park, Stretford, Manchester (M32 0SZ)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1, Merlin Park, Stretford, Manchester (M32 0SZ).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 1, Merlin Park, Stretford, Manchester (M32 0SZ).png</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SPUnits 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB)</t>
+          <t>Units 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB).png</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SPUnits J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN)</t>
+          <t>Units J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN).png</t>
         </is>
       </c>
     </row>

--- a/github_siteplan_links.xlsx
+++ b/github_siteplan_links.xlsx
@@ -443,276 +443,276 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Royal Mail, Papyrus Road, Peterborough, PE4 5PE</t>
+          <t>SPRoyal Mail, Papyrus Road, Peterborough, PE4 5PE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Royal Mail, Papyrus Road, Peterborough, PE4 5PE.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPRoyal Mail, Papyrus Road, Peterborough, PE4 5PE.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ</t>
+          <t>SPBunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Bunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPBunzl, Unit 5, Agecroft Commerce Park, Tally Close, Salford, M27 8WJ.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Yodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX</t>
+          <t>SPYodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Yodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPYodel (InPost) Parcel Hub, 95 Downs Road, Wednesbury, Birmingham, WV13 2PX.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Units 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ</t>
+          <t>SPUnits 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 13-14, Eley Estate, Banksia Rd, Edmonton, N18 3AJ.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Springhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT</t>
+          <t>SPSpringhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Springhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPSpringhead Enterprise Park, Springhead Road, Northfleet, DA11 8GT.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Link 62, Premier Way South, Normanton, WF6 1GX</t>
+          <t>SPLink 62, Premier Way South, Normanton, WF6 1GX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Link 62, Premier Way South, Normanton, WF6 1GX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPLink 62, Premier Way South, Normanton, WF6 1GX.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ash Ridge Road, Almondsbury, BS32 4LB</t>
+          <t>SP Ash Ridge Road, Almondsbury, BS32 4LB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Ash Ridge Road, Almondsbury, BS32 4LB.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPAsh Ridge Road, Almondsbury, BS32 4LB.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Units 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA</t>
+          <t>SPUnits 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 500-660, Skyline 120 Business Park, Great Notley, Braintree, CM77 7AA.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Universal Point, Steelmans Road, Wednesbury (WS10 9UZ)</t>
+          <t>SPUniversal Point, Steelmans Road, Wednesbury (WS10 9UZ)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Universal Point, Steelmans Road, Wednesbury (WS10 9UZ).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUniversal Point, Steelmans Road, Wednesbury (WS10 9UZ).png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Units 6-8, Wells Place, Merstham, Redhill, RH1 3AX</t>
+          <t>SPUnits 6-8, Wells Place, Merstham, Redhill, RH1 3AX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 6-8, Wells Place, Merstham, Redhill, RH1 3AX.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 6-8, Wells Place, Merstham, Redhill, RH1 3AX.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB)</t>
+          <t>SPUnit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Unit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnit 1, Brickyard Lane, Melton, North Ferriby (HU14 3HB).png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF)</t>
+          <t>SPCargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Cargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPCargo 10, Airport Way, London Luton Airport, Luton (LU2 9LF).png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL)</t>
+          <t>SPUnit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Unit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnit 1&amp;2, Addison Way, Great Blakenham, Ipswich (IP6 0RL).png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS</t>
+          <t>SPDukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Dukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPDukes Park Industrial Estate, 2 Beaufort Road, Chelmsford CM2 6PS.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>97-99 Beddington Ln, Croydon (CR0 4TD)</t>
+          <t>SP97-99 Beddington Ln, Croydon (CR0 4TD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/97-99 Beddington Ln, Croydon (CR0 4TD).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SP97-99 Beddington Ln, Croydon (CR0 4TD).png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Units 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA)</t>
+          <t>SPUnits 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1-7, Mill Lane Trading Estate, Croydon (CR0 4AA).png</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Units 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN</t>
+          <t>SPUnits 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 6, 6a, 12a, 12b, 12c and 12d, Eurolink Industrial Centre, Sittingbourne, ME10 3RN.png</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE</t>
+          <t>SPHanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Hanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPHanbury Road, Widford Industrial Estate, Chelmsford, CM1 3AE.png</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sinclair Drive, Wellingborough, NN8 6UW</t>
+          <t>SPSinclair Drive, Wellingborough, NN8 6UW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Sinclair Drive, Wellingborough, NN8 6UW.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPSinclair Drive, Wellingborough, NN8 6UW.png</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Axis 40, Athlon Industrial Estate, Wembley, HA0 1YJ</t>
+          <t>SPAxis 40, Athlon Industrial Estate, Wembley, HA0 1YJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Axis 40, Athlon Industrial Estate, Wembley, HA0 1YJ.png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPAxis 40, Athlon Industrial Estate, Wembley, HA0 1YJ.png</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Units 1, Merlin Park, Stretford, Manchester (M32 0SZ)</t>
+          <t>SPUnits 1, Merlin Park, Stretford, Manchester (M32 0SZ)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 1, Merlin Park, Stretford, Manchester (M32 0SZ).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1, Merlin Park, Stretford, Manchester (M32 0SZ).png</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Units 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB)</t>
+          <t>SPUnits 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits 1-2 Lydiard Fields, Great Western Way, Lydiard Tregoze, Swindon (SN5 8UB).png</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Units J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN)</t>
+          <t>SPUnits J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/Units J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN).png</t>
+          <t>https://raw.githubusercontent.com/H1470/KennedyWilsonGithub/main/Images/SPUnits J1 to J4 and Unit L, Stadium Way, Benfleet (SS7 3BN).png</t>
         </is>
       </c>
     </row>
